--- a/tiflow-diga/develop/0.9.0/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
+++ b/tiflow-diga/develop/0.9.0/StructureDefinition-GEM-ERP-PR-MedicationDispense-DiGA.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3660" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3654" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -439,7 +439,7 @@
     <t>MedicationDispense.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -477,7 +477,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -511,7 +511,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -554,7 +554,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -756,10 +756,7 @@
 </t>
   </si>
   <si>
-    <t>An identifier intended for computation</t>
-  </si>
-  <si>
-    <t>An identifier - identifies some entity uniquely and unambiguously. Typically this is used for business identifiers.</t>
+    <t>External identifier</t>
   </si>
   <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
@@ -777,9 +774,6 @@
 </t>
   </si>
   <si>
-    <t>External identifier</t>
-  </si>
-  <si>
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="https://gematik.de/fhir/erp/NamingSystem/GEM_ERP_NS_PrescriptionId"/&gt;
 &lt;/valueIdentifier&gt;</t>
@@ -788,7 +782,7 @@
     <t>MedicationDispense.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Procedure)
+    <t xml:space="preserve">Reference(Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -826,9 +820,6 @@
     <t>required</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the dispense event.</t>
-  </si>
-  <si>
     <t>https://gematik.de/fhir/terminology/ValueSet/ti-medication-dispense-status-vs</t>
   </si>
   <si>
@@ -848,7 +839,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.0.1)</t>
   </si>
   <si>
     <t>Why a dispense was not performed</t>
@@ -860,7 +851,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +986,7 @@
     <t>Value of extension</t>
   </si>
   <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
   </si>
   <si>
     <t>asked-declined</t>
@@ -1005,6 +996,10 @@
   </si>
   <si>
     <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
   </si>
   <si>
     <t>MedicationDispense.medication[x].reference</t>
@@ -1196,15 +1191,7 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
     <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>Role.effectiveTime or implied by context</t>
@@ -1293,9 +1280,6 @@
     <t>MedicationDispense.subject.type</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
-  </si>
-  <si>
     <t>MedicationDispense.subject.identifier</t>
   </si>
   <si>
@@ -1303,6 +1287,9 @@
 </t>
   </si>
   <si>
+    <t>Logical reference, when literal reference is not known</t>
+  </si>
+  <si>
     <t>MedicationDispense.subject.display</t>
   </si>
   <si>
@@ -1312,7 +1299,7 @@
     <t>MedicationDispense.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1331,7 +1318,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1407,7 +1394,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.0.1</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1451,16 +1438,13 @@
 </t>
   </si>
   <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
     <t>MedicationDispense.performer.actor.display</t>
   </si>
   <si>
     <t>MedicationDispense.location</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -1476,7 +1460,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1543,7 +1527,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1649,7 +1633,7 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
@@ -1704,123 +1688,6 @@
 The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-DosageStructuredOrFreeTextWarning:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresBoth:Wenn eine strukturierte Dosierungsangabe erfolgt, müssen sowohl timing als auch doseAndRate angegeben werden. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (timing.exists() implies doseAndRate.exists()) and
-  (doseAndRate.exists() implies timing.exists())
-)
-}DosageDoseUnitSameCode:Die Dosiereinheit muss über alle Dosierungen gleich sein. {(%resource.ofType(MedicationRequest).dosageInstruction | ofType(MedicationDispense).dosageInstruction | ofType(MedicationStatement).dosage).all(
-doseAndRate.exists() implies
-  (
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Quantity).code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).low.code | 
-    %resource.dosageInstruction.doseAndRate.dose.ofType(Range).high.code
-  ).distinct().count() = 1
-)}DosageWarnungViererschemaInText:Hinweis: In Dosage.text wurde ein Viererschema (z. B. 1-1-1-1) erkannt. Bitte prüfen, ob dies strukturiert abgebildet werden kann. {text.exists() implies text.matches('.*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\s*\\d+\\s*[-–]\\d+.*').not()}FreeTextSingleDosageOnlyWarning:Wenn eine Dosierung als reiner Freitext angegeben ist, soll nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}DosageStructuredOrFreeText:Die Dosierungsangabe darf entweder nur als Freitext oder nur als vollständige strukturierte Information erfolgen — eine Mischung ist nicht erlaubt. {(%resource.ofType(MedicationRequest).dosageInstruction | 
- ofType(MedicationDispense).dosageInstruction | 
- ofType(MedicationStatement).dosage).all(
-  (text.exists() and timing.empty() and doseAndRate.empty()) or
-  (text.empty() and (timing.exists() or doseAndRate.exists()))
-)
-}DosageStructuredRequiresGeneratedText:Liegt eine strukturierte Dosierungsangabe vor (timing und doseAndRate belegt, text leer), muss die Extension GeneratedDosageInstructionsMeta vorhanden sein. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(timing.exists() and doseAndRate.exists() and text.empty())
-)
-implies
-(
-%resource.extension.where(
-  url = 'http://ig.fhir.de/igs/medication/StructureDefinition/GeneratedDosageInstructionsMeta'
-).exists() and
-(
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-  ).exists() or
-  %resource.extension.where(
-    url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-  ).exists()
-)
-)
-}FreeTextSingleDosageOnly:Wenn eine Dosierung als reiner Freitext angegeben ist, darf nur genau ein Dosage-Element existieren. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).exists(text.exists() and timing.empty() and doseAndRate.empty())
-)
-implies
-(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).count() = 1
-)}FreeTextMatchesRenderedText:Wenn eine Dosierung als reiner Freitext angegeben ist (text vorhanden, timing und doseAndRate leer) UND die Extension renderedDosageInstruction befüllt ist, muss der Wert in dosageInstruction.text mit dem Wert in der Extension übereinstimmen. {(
-  (%resource.ofType(MedicationRequest).dosageInstruction |
-   %resource.ofType(MedicationDispense).dosageInstruction |
-   %resource.ofType(MedicationStatement).dosage
-  ).where(text.exists() and timing.empty() and doseAndRate.empty()).exists()
-)
-implies
-(
-  (
-    %resource.ofType(MedicationRequest).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationDispense).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.renderedDosageInstruction'
-      ).value = %resource.dosageInstruction.text
-    )
-  ) or
-  (
-    %resource.ofType(MedicationStatement).exists() and
-    (
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).empty() or
-      %resource.extension.where(
-        url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationStatement.renderedDosageInstruction'
-      ).value = %resource.dosage.text
-    )
-  )
-)}</t>
-  </si>
-  <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SBADM, moodCode=INT]</t>
   </si>
   <si>
@@ -1912,7 +1779,7 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -1935,7 +1802,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.0.1)
 </t>
   </si>
   <si>
@@ -1954,7 +1821,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -4331,7 +4198,7 @@
         <v>195</v>
       </c>
       <c r="D18" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4358,9 +4225,7 @@
       <c r="M18" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="N18" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4418,7 +4283,7 @@
         <v>80</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>117</v>
@@ -4427,7 +4292,7 @@
         <v>78</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>78</v>
@@ -4450,7 +4315,7 @@
         <v>200</v>
       </c>
       <c r="D19" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4477,9 +4342,7 @@
       <c r="M19" t="s" s="2">
         <v>203</v>
       </c>
-      <c r="N19" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>78</v>
@@ -4569,7 +4432,7 @@
         <v>205</v>
       </c>
       <c r="D20" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4596,9 +4459,7 @@
       <c r="M20" t="s" s="2">
         <v>208</v>
       </c>
-      <c r="N20" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>78</v>
@@ -4656,7 +4517,7 @@
         <v>80</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>117</v>
@@ -5181,7 +5042,7 @@
         <v>236</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="N25" t="s" s="2">
         <v>226</v>
@@ -5195,7 +5056,7 @@
         <v>78</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>78</v>
@@ -5266,13 +5127,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>222</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
@@ -5294,10 +5155,10 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="M26" t="s" s="2">
         <v>225</v>
@@ -5314,7 +5175,7 @@
         <v>78</v>
       </c>
       <c r="S26" t="s" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="T26" t="s" s="2">
         <v>78</v>
@@ -5385,10 +5246,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5411,16 +5272,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5470,7 +5331,7 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
@@ -5482,13 +5343,13 @@
         <v>150</v>
       </c>
       <c r="AJ27" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AK27" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="AK27" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AL27" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>78</v>
@@ -5502,10 +5363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5531,13 +5392,13 @@
         <v>167</v>
       </c>
       <c r="L28" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="N28" t="s" s="2">
         <v>253</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5545,7 +5406,7 @@
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>78</v>
@@ -5563,13 +5424,11 @@
         <v>78</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="Y28" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>78</v>
@@ -5587,7 +5446,7 @@
         <v>78</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>88</v>
@@ -5602,16 +5461,16 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="AL28" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>262</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5619,10 +5478,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5645,13 +5504,13 @@
         <v>78</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5681,10 +5540,10 @@
         <v>157</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>78</v>
@@ -5702,7 +5561,7 @@
         <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -5717,10 +5576,10 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>78</v>
@@ -5734,10 +5593,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5760,16 +5619,16 @@
         <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5795,13 +5654,13 @@
         <v>78</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>78</v>
@@ -5819,7 +5678,7 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -5837,7 +5696,7 @@
         <v>78</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>78</v>
@@ -5846,15 +5705,15 @@
         <v>78</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5877,16 +5736,16 @@
         <v>89</v>
       </c>
       <c r="K31" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="M31" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>284</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5936,7 +5795,7 @@
         <v>78</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>88</v>
@@ -5951,27 +5810,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>289</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6083,10 +5942,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6200,13 +6059,13 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C34" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D34" t="s" s="2">
         <v>78</v>
@@ -6228,13 +6087,13 @@
         <v>78</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -6303,7 +6162,7 @@
         <v>78</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>78</v>
@@ -6317,10 +6176,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6343,7 +6202,7 @@
         <v>78</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>103</v>
@@ -6409,7 +6268,7 @@
         <v>88</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>78</v>
+        <v>150</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>78</v>
@@ -6432,14 +6291,14 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -6461,14 +6320,12 @@
         <v>109</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>112</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6535,7 +6392,7 @@
         <v>78</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>78</v>
@@ -6549,10 +6406,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6578,13 +6435,13 @@
         <v>130</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6592,7 +6449,7 @@
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>78</v>
@@ -6634,7 +6491,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>88</v>
@@ -6666,10 +6523,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6695,10 +6552,10 @@
         <v>167</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6710,7 +6567,7 @@
         <v>78</v>
       </c>
       <c r="S38" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="T38" t="s" s="2">
         <v>78</v>
@@ -6725,11 +6582,11 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y38" s="2"/>
       <c r="Z38" t="s" s="2">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -6747,7 +6604,7 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6756,7 +6613,7 @@
         <v>88</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>150</v>
+        <v>313</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>100</v>
@@ -6779,10 +6636,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6808,13 +6665,13 @@
         <v>102</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6864,7 +6721,7 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6873,7 +6730,7 @@
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>100</v>
@@ -6896,10 +6753,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6925,13 +6782,13 @@
         <v>130</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N40" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6960,28 +6817,28 @@
         <v>146</v>
       </c>
       <c r="Y40" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -7013,10 +6870,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7042,13 +6899,13 @@
         <v>223</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="N41" t="s" s="2">
         <v>330</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -7098,7 +6955,7 @@
         <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -7107,7 +6964,7 @@
         <v>88</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>100</v>
@@ -7116,7 +6973,7 @@
         <v>78</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>78</v>
@@ -7125,15 +6982,15 @@
         <v>78</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7245,10 +7102,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7362,10 +7219,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7391,16 +7248,16 @@
         <v>167</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="N44" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>341</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>78</v>
@@ -7425,31 +7282,31 @@
         <v>78</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF44" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>344</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>79</v>
@@ -7467,7 +7324,7 @@
         <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>78</v>
@@ -7481,10 +7338,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7507,19 +7364,19 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>347</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>348</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
@@ -7547,29 +7404,29 @@
         <v>146</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF45" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AG45" t="s" s="2">
         <v>79</v>
       </c>
@@ -7577,7 +7434,7 @@
         <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>100</v>
@@ -7586,7 +7443,7 @@
         <v>78</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>78</v>
@@ -7595,15 +7452,15 @@
         <v>78</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7629,65 +7486,65 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="N46" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF46" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -7705,7 +7562,7 @@
         <v>78</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>78</v>
@@ -7714,15 +7571,15 @@
         <v>78</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7748,13 +7605,13 @@
         <v>102</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N47" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>368</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7768,7 +7625,7 @@
         <v>78</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>78</v>
@@ -7804,7 +7661,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7822,7 +7679,7 @@
         <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>78</v>
@@ -7831,15 +7688,15 @@
         <v>78</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7862,17 +7719,15 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="L48" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>377</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>78</v>
@@ -7921,7 +7776,7 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7930,16 +7785,16 @@
         <v>88</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>379</v>
+        <v>100</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>78</v>
@@ -7948,15 +7803,15 @@
         <v>78</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7979,16 +7834,16 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8038,7 +7893,7 @@
         <v>78</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -8047,16 +7902,16 @@
         <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>249</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>78</v>
@@ -8065,15 +7920,15 @@
         <v>78</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8099,13 +7954,13 @@
         <v>102</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8155,7 +8010,7 @@
         <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -8187,10 +8042,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8213,16 +8068,16 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8272,7 +8127,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>79</v>
@@ -8284,30 +8139,30 @@
         <v>150</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8419,10 +8274,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8536,10 +8391,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8565,13 +8420,13 @@
         <v>102</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N54" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8621,7 +8476,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>79</v>
@@ -8630,7 +8485,7 @@
         <v>88</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>100</v>
@@ -8653,10 +8508,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8682,13 +8537,13 @@
         <v>130</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8717,28 +8572,28 @@
         <v>146</v>
       </c>
       <c r="Y55" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF55" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>79</v>
@@ -8770,10 +8625,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8796,16 +8651,16 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>236</v>
+        <v>406</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>237</v>
+        <v>329</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8855,7 +8710,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>79</v>
@@ -8873,7 +8728,7 @@
         <v>78</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>78</v>
@@ -8887,10 +8742,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8916,13 +8771,13 @@
         <v>102</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8972,7 +8827,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>79</v>
@@ -9004,10 +8859,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9030,16 +8885,16 @@
         <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9089,7 +8944,7 @@
         <v>78</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>79</v>
@@ -9101,13 +8956,13 @@
         <v>150</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>78</v>
@@ -9121,10 +8976,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9147,16 +9002,16 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9206,7 +9061,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>79</v>
@@ -9218,16 +9073,16 @@
         <v>150</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>78</v>
@@ -9238,10 +9093,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9264,13 +9119,13 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9321,7 +9176,7 @@
         <v>78</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>79</v>
@@ -9336,10 +9191,10 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>78</v>
@@ -9353,10 +9208,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9468,10 +9323,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9585,14 +9440,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9614,10 +9469,10 @@
         <v>109</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="N63" t="s" s="2">
         <v>112</v>
@@ -9672,7 +9527,7 @@
         <v>78</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>79</v>
@@ -9704,10 +9559,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9730,19 +9585,19 @@
         <v>78</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
@@ -9770,10 +9625,10 @@
         <v>157</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>78</v>
@@ -9791,7 +9646,7 @@
         <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>79</v>
@@ -9809,7 +9664,7 @@
         <v>78</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>78</v>
@@ -9818,15 +9673,15 @@
         <v>78</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9849,16 +9704,16 @@
         <v>78</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9908,7 +9763,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>88</v>
@@ -9920,13 +9775,13 @@
         <v>150</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>78</v>
@@ -9940,10 +9795,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10055,10 +9910,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10172,10 +10027,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10201,13 +10056,13 @@
         <v>102</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10257,7 +10112,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>79</v>
@@ -10266,7 +10121,7 @@
         <v>88</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>100</v>
@@ -10289,10 +10144,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10318,13 +10173,13 @@
         <v>130</v>
       </c>
       <c r="L69" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N69" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M69" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10353,28 +10208,28 @@
         <v>146</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>79</v>
@@ -10406,10 +10261,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10432,16 +10287,16 @@
         <v>89</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10491,7 +10346,7 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>79</v>
@@ -10500,7 +10355,7 @@
         <v>88</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>100</v>
@@ -10509,7 +10364,7 @@
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>78</v>
@@ -10518,15 +10373,15 @@
         <v>78</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>232</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10552,13 +10407,13 @@
         <v>102</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10608,7 +10463,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>79</v>
@@ -10640,10 +10495,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10666,16 +10521,16 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10725,7 +10580,7 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>79</v>
@@ -10737,13 +10592,13 @@
         <v>150</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>78</v>
@@ -10757,10 +10612,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10783,16 +10638,16 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10842,7 +10697,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>79</v>
@@ -10854,30 +10709,30 @@
         <v>150</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10989,10 +10844,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11106,10 +10961,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11135,13 +10990,13 @@
         <v>102</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N76" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11191,7 +11046,7 @@
         <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>79</v>
@@ -11200,7 +11055,7 @@
         <v>88</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>100</v>
@@ -11223,10 +11078,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11252,13 +11107,13 @@
         <v>130</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="N77" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>325</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11287,28 +11142,28 @@
         <v>146</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>326</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>328</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>79</v>
@@ -11340,10 +11195,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11369,13 +11224,13 @@
         <v>223</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>458</v>
+        <v>406</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11425,7 +11280,7 @@
         <v>78</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>79</v>
@@ -11443,7 +11298,7 @@
         <v>78</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>78</v>
@@ -11457,10 +11312,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11486,13 +11341,13 @@
         <v>102</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11542,7 +11397,7 @@
         <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>79</v>
@@ -11574,10 +11429,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11600,16 +11455,16 @@
         <v>78</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11638,10 +11493,10 @@
         <v>157</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>78</v>
@@ -11659,7 +11514,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>79</v>
@@ -11677,24 +11532,24 @@
         <v>78</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11717,16 +11572,16 @@
         <v>78</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11776,7 +11631,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>79</v>
@@ -11788,30 +11643,30 @@
         <v>150</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11834,16 +11689,16 @@
         <v>78</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11893,7 +11748,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>79</v>
@@ -11905,13 +11760,13 @@
         <v>150</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>78</v>
@@ -11920,15 +11775,15 @@
         <v>78</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11951,13 +11806,13 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12008,7 +11863,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>79</v>
@@ -12026,24 +11881,24 @@
         <v>78</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12066,13 +11921,13 @@
         <v>78</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -12123,42 +11978,42 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="AL84" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="AG84" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>513</v>
-      </c>
       <c r="AM84" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12181,16 +12036,16 @@
         <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12240,7 +12095,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>79</v>
@@ -12252,30 +12107,30 @@
         <v>150</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12298,16 +12153,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12357,7 +12212,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>79</v>
@@ -12369,19 +12224,19 @@
         <v>150</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
@@ -12389,10 +12244,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12415,16 +12270,16 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12474,7 +12329,7 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>79</v>
@@ -12489,10 +12344,10 @@
         <v>100</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>78</v>
@@ -12501,15 +12356,15 @@
         <v>78</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12532,16 +12387,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12591,7 +12446,7 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>79</v>
@@ -12600,16 +12455,16 @@
         <v>80</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>150</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>538</v>
+        <v>100</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>78</v>
@@ -12623,10 +12478,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12649,16 +12504,16 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12708,7 +12563,7 @@
         <v>78</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>79</v>
@@ -12726,13 +12581,13 @@
         <v>78</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -12740,10 +12595,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12855,10 +12710,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12972,14 +12827,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13001,10 +12856,10 @@
         <v>109</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>112</v>
@@ -13059,7 +12914,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>79</v>
@@ -13091,10 +12946,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13117,13 +12972,13 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13174,7 +13029,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>88</v>
@@ -13192,7 +13047,7 @@
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>553</v>
+        <v>547</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>78</v>
@@ -13206,10 +13061,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13232,16 +13087,16 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13270,10 +13125,10 @@
         <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13291,7 +13146,7 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>79</v>
@@ -13309,24 +13164,24 @@
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>560</v>
+        <v>554</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13349,16 +13204,16 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13387,10 +13242,10 @@
         <v>157</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>78</v>
@@ -13408,7 +13263,7 @@
         <v>78</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>79</v>
@@ -13426,24 +13281,24 @@
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13466,16 +13321,16 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>569</v>
+        <v>563</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13525,7 +13380,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>79</v>
@@ -13537,19 +13392,19 @@
         <v>150</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -13557,14 +13412,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -13583,16 +13438,16 @@
         <v>78</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>577</v>
+        <v>571</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13642,7 +13497,7 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>79</v>
@@ -13654,13 +13509,13 @@
         <v>150</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>78</v>
@@ -13674,10 +13529,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13700,16 +13555,16 @@
         <v>78</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13759,7 +13614,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>79</v>
@@ -13771,13 +13626,13 @@
         <v>150</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>78</v>
